--- a/outputs/weekly-tracker.xlsx
+++ b/outputs/weekly-tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Posts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Posts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -835,6 +835,49 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Minimalist</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>minimalist_niacinamide-10-serum-pdp</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CRO Fix</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>outputs/cro-fixes/minimalist_niacinamide-10-serum-pdp_carousel.html</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PRODUCT PAGE (PDP): Minimalist's Niacinamide 10% serum page opens on a really good studio photo. On a phone, that photo is the entire first screen.
+The product name starts right at the bottom edge....</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/weekly-tracker.xlsx
+++ b/outputs/weekly-tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Posts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Posts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -878,6 +878,49 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fly By Jing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flybyjing_chili-crisp-pdp</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CRO Fix</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>outputs/cro-fixes/flybyjing_chili-crisp-pdp_carousel.html</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PRODUCT PAGE (PDP): Fly By Jing's chili crisp page, on a phone. Screen one is the jar, the name, five stars and a paragraph. No price.
+The price shows up 1,146px down and Add to Cart at 1,357px. The...</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/weekly-tracker.xlsx
+++ b/outputs/weekly-tracker.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -921,6 +921,92 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bala</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bala_bangles-homepage</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CRO Fix</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>outputs/cro-fixes/bala_bangles-homepage_carousel.html</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>HOMEPAGE: Bala's homepage, on a phone. Screen one is "Fitness, but make it cute" in a hairline font, a 10% bundle discount and an outline button. It never says what Bala sells.
+The blue bands on the...</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Topicals</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>topicals_homepage-hero</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CRO Fix</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>outputs/cro-fixes/topicals_homepage-hero_carousel.html</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>HOMEPAGE: Open Topicals on a phone and the first thing you get is a scratch card. "Try your luck. Scratch below to see what you win."
+Close it and you get the TOPICALS wordmark, a face, and a promo...</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/weekly-tracker.xlsx
+++ b/outputs/weekly-tracker.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1007,49 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fishwife</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fishwife_shop-all-collection</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CRO Fix</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>outputs/cro-fixes/fishwife_shop-all-collection_carousel.html</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>COLLECTION PAGE: Fishwife's shop-all page has one job on a phone. Help someone pick a tin.
+On a 390px screen, the first 400px under the header is a banner that says "Shop Tinned Fish &amp; More!" The...</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
